--- a/Outputs/Scenarios/PtX_demand_LV_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LV_Electrification.xlsx
@@ -507,7 +507,7 @@
         <v>0.002408716174825779</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004671275484928</v>
+        <v>0.0004671275484928001</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0.0195930929982781</v>
       </c>
       <c r="G11" t="n">
-        <v>8.12449026753831e-05</v>
+        <v>8.124490267538311e-05</v>
       </c>
       <c r="H11" t="n">
         <v>0.0074870826105117</v>
@@ -1568,7 +1568,7 @@
         <v>2050</v>
       </c>
       <c r="C31" t="n">
-        <v>6.674077694726495e-06</v>
+        <v>6.674077694726497e-06</v>
       </c>
       <c r="D31" t="n">
         <v>3.205674398439927e-05</v>

--- a/Outputs/Scenarios/PtX_demand_LV_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LV_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001613032710587493</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002301956299606777</v>
+        <v>0.002448378737498125</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0003836593832677962</v>
+        <v>0.0005084830399946095</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001534637533071185</v>
+        <v>0.002033932159978438</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.002301956299606777</v>
+        <v>0.002033932159978438</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0001292687422421981</v>
       </c>
       <c r="K24" t="n">
-        <v>0.003185633512392048</v>
+        <v>0.003127519426176728</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0007824639687501922</v>
       </c>
       <c r="K25" t="n">
-        <v>0.03120320778208645</v>
+        <v>0.03063398162967788</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>2.324107095311647e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0003836593832677962</v>
+        <v>0.0005084830399946095</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.002387898547100426</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01355373631022544</v>
+        <v>0.0132153558424388</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.002258956051704241</v>
+        <v>0.002744585308823754</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.009035824206816962</v>
+        <v>0.01097834123529502</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01355373631022544</v>
+        <v>0.01097834123529502</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001256788709000225</v>
       </c>
       <c r="K42" t="n">
-        <v>0.002258956051704241</v>
+        <v>0.002744585308823754</v>
       </c>
     </row>
     <row r="43">
